--- a/assets/welding_cart_cut_list.xlsx
+++ b/assets/welding_cart_cut_list.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
   <si>
     <t xml:space="preserve">Part</t>
   </si>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Front column</t>
   </si>
   <si>
-    <t xml:space="preserve">Front columns; outer-wall tab notch at bottom rail only, open top under plywood</t>
+    <t xml:space="preserve">Front columns; full height, plain square cuts, open top under plywood</t>
   </si>
   <si>
     <t xml:space="preserve">Rear column</t>
@@ -57,22 +57,16 @@
     <t xml:space="preserve">Rear columns; sit on bottom side rails, open top under plywood</t>
   </si>
   <si>
-    <t xml:space="preserve">Rail 25.76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front bottom rail between column outer-wall tabs (W - 2 x 0.120 wall)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rail 23.00</t>
   </si>
   <si>
-    <t xml:space="preserve">Front and rear top, front and rear mid, rear bottom, back cross rail (W - 2 x 1.5)</t>
+    <t xml:space="preserve">Front and rear top, front and rear mid, front and rear bottom, back cross rail (W - 2 x 1.5)</t>
   </si>
   <si>
     <t xml:space="preserve">Bottom side rail</t>
   </si>
   <si>
-    <t xml:space="preserve">Front column inner face to rear end; end tab covers hole</t>
+    <t xml:space="preserve">Front column inner face to rear end; end cap covers hole</t>
   </si>
   <si>
     <t xml:space="preserve">Side rail 21.00</t>
@@ -617,7 +611,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -708,21 +702,21 @@
         <v>11</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>25.76</v>
+        <v>23</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">B4*C4</f>
-        <v>25.76</v>
+        <v>161</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="2" t="n">
         <f aca="false">COUNTIF('Bar Plan'!$C$2:$C$18,A4)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G4" s="2" t="str">
         <f aca="false">IF(F4=B4,"OK","CHECK")</f>
@@ -734,21 +728,21 @@
         <v>13</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>23</v>
+        <v>30.5</v>
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">B5*C5</f>
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="n">
         <f aca="false">COUNTIF('Bar Plan'!$C$2:$C$18,A5)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2" t="str">
         <f aca="false">IF(F5=B5,"OK","CHECK")</f>
@@ -760,21 +754,21 @@
         <v>15</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>30.5</v>
+        <v>21</v>
       </c>
       <c r="D6" s="5" t="n">
         <f aca="false">B6*C6</f>
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="2" t="n">
         <f aca="false">COUNTIF('Bar Plan'!$C$2:$C$18,A6)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="2" t="str">
         <f aca="false">IF(F6=B6,"OK","CHECK")</f>
@@ -782,51 +776,25 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <f aca="false">B7*C7</f>
-        <v>84</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="B7" s="6" t="n">
+        <f aca="false">SUM(B2:B6)</f>
+        <v>17</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <f aca="false">SUM(D2:D6)</f>
+        <v>455</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <f aca="false">SUM(F2:F6)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
         <v>18</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <f aca="false">COUNTIF('Bar Plan'!$C$2:$C$18,A7)</f>
-        <v>4</v>
-      </c>
-      <c r="G7" s="2" t="str">
-        <f aca="false">IF(F7=B7,"OK","CHECK")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="6" t="n">
-        <f aca="false">SUM(B2:B7)</f>
-        <v>17</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <f aca="false">SUM(D2:D7)</f>
-        <v>457.76</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <f aca="false">SUM(F2:F7)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -855,59 +823,59 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>120</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>0.125</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -943,10 +911,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -955,28 +923,28 @@
         <v>2</v>
       </c>
       <c r="F1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="J1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="K1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="L1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="M1" s="15" t="s">
         <v>38</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -990,7 +958,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C2,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C2,Parts!$A$2:$A$6,0))</f>
         <v>38</v>
       </c>
       <c r="F2" s="2" t="n">
@@ -1036,7 +1004,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C3,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C3,Parts!$A$2:$A$6,0))</f>
         <v>38</v>
       </c>
       <c r="F3" s="2" t="n">
@@ -1082,7 +1050,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C4,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C4,Parts!$A$2:$A$6,0))</f>
         <v>36.5</v>
       </c>
       <c r="F4" s="2" t="n">
@@ -1094,7 +1062,7 @@
       </c>
       <c r="H4" s="5" t="n">
         <f aca="false">SUMIF($A$2:$A$18,F4,$D$2:$D$18)</f>
-        <v>117.76</v>
+        <v>115</v>
       </c>
       <c r="I4" s="5" t="n">
         <f aca="false">(G4-1)*Assumptions!$B$5</f>
@@ -1102,15 +1070,15 @@
       </c>
       <c r="J4" s="5" t="n">
         <f aca="false">H4+I4</f>
-        <v>118.26</v>
+        <v>115.5</v>
       </c>
       <c r="K4" s="5" t="n">
         <f aca="false">Assumptions!$B$4-J4</f>
-        <v>1.73999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="L4" s="5" t="n">
         <f aca="false">K4-Assumptions!$B$6</f>
-        <v>1.23999999999999</v>
+        <v>4</v>
       </c>
       <c r="M4" s="2" t="str">
         <f aca="false">IF(L4&gt;=0,"OK","TOO LONG")</f>
@@ -1128,7 +1096,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C5,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C5,Parts!$A$2:$A$6,0))</f>
         <v>36.5</v>
       </c>
       <c r="F5" s="2" t="n">
@@ -1171,14 +1139,14 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C6,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C6,Parts!$A$2:$A$6,0))</f>
         <v>30.5</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G6" s="16" t="n">
         <f aca="false">SUM(G2:G5)</f>
@@ -1186,11 +1154,11 @@
       </c>
       <c r="H6" s="7" t="n">
         <f aca="false">SUM(H2:H5)</f>
-        <v>457.76</v>
+        <v>455</v>
       </c>
       <c r="K6" s="7" t="n">
         <f aca="false">SUM(K2:K5)</f>
-        <v>20.615</v>
+        <v>23.375</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1201,10 +1169,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C7,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C7,Parts!$A$2:$A$6,0))</f>
         <v>30.5</v>
       </c>
     </row>
@@ -1216,14 +1184,14 @@
         <v>4</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C8,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C8,Parts!$A$2:$A$6,0))</f>
         <v>21</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G8" s="10" t="n">
         <f aca="false">COUNT(F2:F5)</f>
@@ -1241,15 +1209,15 @@
         <v>11</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C9,Parts!$A$2:$A$7,0))</f>
-        <v>25.76</v>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C9,Parts!$A$2:$A$6,0))</f>
+        <v>23</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G9" s="17" t="n">
         <f aca="false">H6/(G8*Assumptions!B4)</f>
-        <v>0.953666666666667</v>
+        <v>0.947916666666667</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1260,10 +1228,10 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C10,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C10,Parts!$A$2:$A$6,0))</f>
         <v>23</v>
       </c>
     </row>
@@ -1275,14 +1243,14 @@
         <v>3</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C11,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C11,Parts!$A$2:$A$6,0))</f>
         <v>23</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1293,10 +1261,10 @@
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C12,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C12,Parts!$A$2:$A$6,0))</f>
         <v>23</v>
       </c>
     </row>
@@ -1308,10 +1276,10 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D13" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C13,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C13,Parts!$A$2:$A$6,0))</f>
         <v>23</v>
       </c>
     </row>
@@ -1323,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C14,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C14,Parts!$A$2:$A$6,0))</f>
         <v>23</v>
       </c>
     </row>
@@ -1338,10 +1306,10 @@
         <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D15" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C15,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C15,Parts!$A$2:$A$6,0))</f>
         <v>23</v>
       </c>
     </row>
@@ -1353,10 +1321,10 @@
         <v>3</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D16" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C16,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C16,Parts!$A$2:$A$6,0))</f>
         <v>21</v>
       </c>
     </row>
@@ -1368,10 +1336,10 @@
         <v>4</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D17" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C17,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C17,Parts!$A$2:$A$6,0))</f>
         <v>21</v>
       </c>
     </row>
@@ -1383,10 +1351,10 @@
         <v>5</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D18" s="5" t="n">
-        <f aca="false">INDEX(Parts!$C$2:$C$7,MATCH(C18,Parts!$A$2:$A$7,0))</f>
+        <f aca="false">INDEX(Parts!$C$2:$C$6,MATCH(C18,Parts!$A$2:$A$6,0))</f>
         <v>21</v>
       </c>
     </row>

--- a/assets/welding_cart_cut_list.xlsx
+++ b/assets/welding_cart_cut_list.xlsx
@@ -57,10 +57,10 @@
     <t xml:space="preserve">Rear columns; sit on bottom side rails, open top under plywood</t>
   </si>
   <si>
-    <t xml:space="preserve">Rail 23.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front and rear top, front and rear mid, front and rear bottom, back cross rail (W - 2 x 1.5)</t>
+    <t xml:space="preserve">Rail 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front and rear top, front and rear mid, front and rear bottom, back cross rail (26 - 2 x 1-1/2)</t>
   </si>
   <si>
     <t xml:space="preserve">Bottom side rail</t>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Front column inner face to rear end; end cap covers hole</t>
   </si>
   <si>
-    <t xml:space="preserve">Side rail 21.00</t>
+    <t xml:space="preserve">Side rail 21</t>
   </si>
   <si>
     <t xml:space="preserve">Top side rails (2) and mid side rails (2)</t>
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Lengths are cut lengths for the 26" wide x 24" deep (outside) frame with 8" tank shelf, 16.00" clear openings above 3/4" plywood, 1.5" tube.</t>
+    <t xml:space="preserve">Lengths are cut lengths for the 26" wide x 24" deep (outside) frame with 8" tank shelf, 16" clear openings above 3/4" plywood, 1-1/2" tube. All lengths shown to the nearest 1/16".</t>
   </si>
   <si>
     <t xml:space="preserve">Welding cart - 10 ft bar stock cut plan</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Tube</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5" x 1.5" x 11 ga (0.120" wall)</t>
+    <t xml:space="preserve">1-1/2" x 1-1/2" x 11 ga</t>
   </si>
   <si>
     <t xml:space="preserve">Casters (4) are not cut from bar stock and are not in this plan.</t>
@@ -147,20 +147,18 @@
     <t xml:space="preserve">Utilization</t>
   </si>
   <si>
-    <t xml:space="preserve">Cut each bar longest to shortest. Bar 2 is the tight one (1.13" drop before the squaring reserve).</t>
+    <t xml:space="preserve">Cut each bar longest to shortest. Bar 2 is the tight one (1-1/8" drop before the squaring reserve).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="# ??/??\&quot;"/>
+    <numFmt numFmtId="166" formatCode="0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -286,7 +284,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -331,14 +329,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -351,11 +341,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -846,7 +836,7 @@
       <c r="A5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="11" t="n">
         <v>0.125</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -857,7 +847,7 @@
       <c r="A6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="11" t="n">
         <v>0.5</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -868,7 +858,7 @@
       <c r="A7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="12" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="8"/>
@@ -922,28 +912,28 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1148,7 +1138,7 @@
       <c r="F6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="14" t="n">
         <f aca="false">SUM(G2:G5)</f>
         <v>17</v>
       </c>
@@ -1215,7 +1205,7 @@
       <c r="F9" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="15" t="n">
         <f aca="false">H6/(G8*Assumptions!B4)</f>
         <v>0.947916666666667</v>
       </c>
